--- a/src/test/resources/testdata/MyProfileData.xlsx
+++ b/src/test/resources/testdata/MyProfileData.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Gyrus_Selenium_Automation\GyrusAim17_Learner_Automation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821A9593-2920-4554-B889-A7C5245FF002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678B5389-36E2-4873-9D09-9326D71C3587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{740871A2-68D4-459A-A551-7F9AD73C6301}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{740871A2-68D4-459A-A551-7F9AD73C6301}"/>
   </bookViews>
   <sheets>
     <sheet name="ResetPassword" sheetId="1" r:id="rId1"/>
     <sheet name="CFR21Security" sheetId="2" r:id="rId2"/>
+    <sheet name="ValidLogin" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>CurrentPassword</t>
   </si>
@@ -55,6 +56,15 @@
   </si>
   <si>
     <t>ConfirmNew PIN</t>
+  </si>
+  <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>p17 student 06</t>
   </si>
 </sst>
 </file>
@@ -512,4 +522,33 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F003831B-A4D7-4EA0-9D42-AEE6279D3989}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>123</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>